--- a/data/trans_camb/IP1020-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP1020-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,78; 7,61</t>
+          <t>1,83; 7,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,99</t>
+          <t>0,41; 3,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,82; 8,94</t>
+          <t>0,8; 8,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 0,8</t>
+          <t>-4,29; 0,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 3,05</t>
+          <t>-3,44; 2,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,59; -0,56</t>
+          <t>-6,22; -0,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 3,24</t>
+          <t>-0,68; 3,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 2,21</t>
+          <t>-1,26; 2,18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 2,72</t>
+          <t>-1,42; 2,81</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-88,39; 538,2</t>
+          <t>-100,0; 347,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-53,1; 710,3</t>
+          <t>-44,91; 719,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-73,56; 531,55</t>
+          <t>-68,54; 475,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 683,25</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,77; 5,58</t>
+          <t>0,97; 5,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 2,46</t>
+          <t>-0,82; 2,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 6,1</t>
+          <t>0,55; 6,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 3,32</t>
+          <t>-0,24; 3,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 2,58</t>
+          <t>-0,46; 2,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,7; 7,33</t>
+          <t>1,86; 7,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,56</t>
+          <t>0,83; 3,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 1,82</t>
+          <t>-0,38; 1,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,77; 5,54</t>
+          <t>1,68; 5,51</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,07; 1530,99</t>
+          <t>24,65; 1366,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-66,69; 684,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-21,15; 1383,16</t>
+          <t>-8,05; 1570,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-43,56; —</t>
+          <t>-44,38; 1425,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-74,04; —</t>
+          <t>-60,13; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,64; —</t>
+          <t>76,82; 3043,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,69; 701,58</t>
+          <t>43,95; 851,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-38,78; 374,99</t>
+          <t>-42,67; 403,21</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>102,04; 1033,8</t>
+          <t>92,21; 1154,42</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 1,78</t>
+          <t>-2,16; 2,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 1,83</t>
+          <t>-2,25; 1,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 5,72</t>
+          <t>-0,1; 5,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,6; 4,51</t>
+          <t>0,41; 4,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,38; 4,24</t>
+          <t>0,37; 4,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,5; 8,37</t>
+          <t>2,61; 8,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 2,57</t>
+          <t>-0,43; 2,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 2,1</t>
+          <t>-0,32; 2,14</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,87; 5,87</t>
+          <t>2,03; 5,99</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-43,89; —</t>
+          <t>-59,75; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-76,29; —</t>
+          <t>-74,24; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-76,23; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>95,71; —</t>
+          <t>81,81; —</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 1,53</t>
+          <t>-1,39; 1,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 2,45</t>
+          <t>-1,01; 2,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,27; 4,51</t>
+          <t>0,49; 4,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 0,86</t>
+          <t>-1,78; 0,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 2,8</t>
+          <t>-0,91; 2,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 2,78</t>
+          <t>-0,99; 2,62</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 0,64</t>
+          <t>-1,13; 0,83</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 1,94</t>
+          <t>-0,52; 1,93</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,99</t>
+          <t>0,23; 2,87</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-20,41; —</t>
+          <t>-39,55; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-57,44; 831,95</t>
+          <t>-75,89; 859,13</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 247,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-52,49; 545,45</t>
+          <t>-56,94; 676,52</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,24; 892,0</t>
+          <t>3,91; 882,24</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,76; 3,04</t>
+          <t>0,75; 2,97</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 1,47</t>
+          <t>-0,37; 1,38</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,33; 4,18</t>
+          <t>1,36; 4,11</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 1,38</t>
+          <t>-0,41; 1,47</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 1,9</t>
+          <t>-0,2; 1,73</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,64</t>
+          <t>1,19; 3,78</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,85</t>
+          <t>0,4; 1,85</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,04; 1,35</t>
+          <t>0,05; 1,38</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,57; 3,38</t>
+          <t>1,56; 3,39</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>48,72; 745,99</t>
+          <t>53,35; 727,08</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-28,3; 324,19</t>
+          <t>-38,64; 275,26</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>90,64; 920,37</t>
+          <t>91,19; 1030,84</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-38,49; 260,01</t>
+          <t>-37,85; 282,23</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-9,53; 346,06</t>
+          <t>-19,9; 353,11</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,48; 714,68</t>
+          <t>73,47; 683,91</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>37,91; 316,97</t>
+          <t>28,46; 305,26</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 251,82</t>
+          <t>0,32; 236,6</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>149,64; 594,62</t>
+          <t>126,24; 593,56</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1020-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP1020-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,83; 7,29</t>
+          <t>1,85; 7,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,82</t>
+          <t>0,41; 3,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,8; 8,84</t>
+          <t>0,81; 8,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 0,54</t>
+          <t>-4,36; 0,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 2,54</t>
+          <t>-2,95; 3,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,22; -0,57</t>
+          <t>-5,36; -0,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 3,21</t>
+          <t>-0,74; 3,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 2,18</t>
+          <t>-1,33; 2,16</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 2,81</t>
+          <t>-1,49; 2,89</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 347,53</t>
+          <t>-84,68; 489,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-44,91; 719,62</t>
+          <t>-52,11; 742,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-68,54; 475,5</t>
+          <t>-68,18; 610,67</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 683,25</t>
+          <t>-100,0; 633,64</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,97; 5,84</t>
+          <t>0,82; 5,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 2,34</t>
+          <t>-0,97; 2,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 6,12</t>
+          <t>0,28; 5,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 3,24</t>
+          <t>-0,1; 3,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 2,59</t>
+          <t>-0,55; 2,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,86; 7,36</t>
+          <t>1,84; 7,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,65</t>
+          <t>0,89; 3,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 1,84</t>
+          <t>-0,34; 1,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,68; 5,51</t>
+          <t>1,64; 5,82</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>24,65; 1366,61</t>
+          <t>7,7; 1551,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-66,69; 684,17</t>
+          <t>-64,93; 738,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,05; 1570,85</t>
+          <t>-11,73; 1618,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-44,38; 1425,91</t>
+          <t>-37,36; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-60,13; —</t>
+          <t>-65,12; 1136,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,82; 3043,92</t>
+          <t>93,75; 2640,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,95; 851,77</t>
+          <t>45,94; 800,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-42,67; 403,21</t>
+          <t>-33,63; 437,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>92,21; 1154,42</t>
+          <t>95,24; 1236,78</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 2,05</t>
+          <t>-2,15; 2,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 1,86</t>
+          <t>-2,23; 1,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 5,92</t>
+          <t>0,04; 6,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,41; 4,7</t>
+          <t>0,43; 4,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,37; 4,13</t>
+          <t>0,37; 3,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,61; 8,09</t>
+          <t>2,5; 8,14</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 2,41</t>
+          <t>-0,27; 2,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 2,14</t>
+          <t>-0,34; 2,17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,03; 5,99</t>
+          <t>1,96; 5,93</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-59,75; —</t>
+          <t>-44,86; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-74,24; —</t>
+          <t>-62,47; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-65,65; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>81,81; —</t>
+          <t>118,33; —</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 1,47</t>
+          <t>-1,41; 1,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 2,39</t>
+          <t>-1,02; 2,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,78</t>
+          <t>0,38; 4,63</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 0,94</t>
+          <t>-1,86; 0,76</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 2,89</t>
+          <t>-0,93; 2,83</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 2,62</t>
+          <t>-0,67; 2,78</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 0,83</t>
+          <t>-1,26; 0,73</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 1,93</t>
+          <t>-0,67; 2,0</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,87</t>
+          <t>0,45; 3,09</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-39,55; —</t>
+          <t>-33,16; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-75,89; 859,13</t>
+          <t>-63,77; 1107,08</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-56,94; 676,52</t>
+          <t>-63,71; 626,36</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,91; 882,24</t>
+          <t>12,23; 950,74</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,97</t>
+          <t>0,63; 2,92</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 1,38</t>
+          <t>-0,4; 1,38</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,36; 4,11</t>
+          <t>1,24; 3,96</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 1,47</t>
+          <t>-0,33; 1,51</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 1,73</t>
+          <t>-0,0; 1,85</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,78</t>
+          <t>1,24; 3,7</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,85</t>
+          <t>0,49; 2,0</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,05; 1,38</t>
+          <t>0,04; 1,36</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,56; 3,39</t>
+          <t>1,56; 3,44</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>53,35; 727,08</t>
+          <t>36,56; 625,38</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-38,64; 275,26</t>
+          <t>-41,22; 344,38</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>91,19; 1030,84</t>
+          <t>92,72; 916,96</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-37,85; 282,23</t>
+          <t>-30,0; 276,77</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-19,9; 353,11</t>
+          <t>-6,08; 342,84</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,47; 683,91</t>
+          <t>86,73; 683,46</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,46; 305,26</t>
+          <t>38,29; 339,17</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>0,32; 236,6</t>
+          <t>0,36; 230,18</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>126,24; 593,56</t>
+          <t>129,02; 596,11</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1020-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP1020-Edad-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-1,35</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-0,14</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-2,24</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>3,91</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1,36</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3,11</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-1,35</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-0,14</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-2,24</t>
+          <t>3,45</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,31</t>
+          <t>0,56</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,85; 7,96</t>
+          <t>-4,19; 0,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,61</t>
+          <t>-3,42; 3,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,81; 8,82</t>
+          <t>-5,59; -0,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 0,78</t>
+          <t>1,78; 7,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 3,02</t>
+          <t>0,4; 3,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,36; -0,57</t>
+          <t>0,94; 9,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 3,11</t>
+          <t>-0,72; 3,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 2,16</t>
+          <t>-1,39; 2,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 2,89</t>
+          <t>-1,33; 3,41</t>
         </is>
       </c>
     </row>
@@ -730,34 +730,34 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-60,24%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-6,43%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-60,24%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-6,43%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
           <t>101,45%</t>
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>46,65%</t>
         </is>
       </c>
     </row>
@@ -788,24 +788,24 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>-88,39; 538,2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-84,68; 489,8</t>
-        </is>
-      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-52,11; 742,4</t>
+          <t>-53,1; 710,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-68,18; 610,67</t>
+          <t>-73,56; 531,55</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 633,64</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,32</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,89</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4,31</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>2,99</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,55</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2,61</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,32</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,89</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,08</t>
+          <t>2,86</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,39</t>
+          <t>3,61</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,82; 5,66</t>
+          <t>-0,12; 3,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 2,28</t>
+          <t>-0,47; 2,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 5,69</t>
+          <t>1,69; 7,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 3,18</t>
+          <t>0,77; 5,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 2,52</t>
+          <t>-0,9; 2,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,84; 7,54</t>
+          <t>0,49; 6,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,72</t>
+          <t>0,79; 3,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 1,9</t>
+          <t>-0,36; 1,82</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,64; 5,82</t>
+          <t>1,91; 5,91</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>177,25%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>118,92%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>578,26%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>294,69%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>54,49%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>257,28%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>177,25%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>118,92%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>548,35%</t>
+          <t>281,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>385,11%</t>
+          <t>409,56%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,7; 1551,3</t>
+          <t>-43,56; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-64,93; 738,53</t>
+          <t>-74,04; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-11,73; 1618,98</t>
+          <t>78,19; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-37,36; —</t>
+          <t>8,07; 1530,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-65,12; 1136,47</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,75; 2640,45</t>
+          <t>-16,47; 1487,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,94; 800,14</t>
+          <t>40,69; 701,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-33,63; 437,84</t>
+          <t>-38,78; 374,99</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>95,24; 1236,78</t>
+          <t>108,45; 1087,18</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,83</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1,67</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4,9</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,09</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-0,0</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2,69</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,83</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,67</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,79</t>
+          <t>2,84</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3,82</t>
+          <t>3,93</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 2,03</t>
+          <t>0,6; 4,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 1,75</t>
+          <t>0,38; 4,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,04; 6,01</t>
+          <t>2,54; 8,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,65</t>
+          <t>-2,15; 1,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,88</t>
+          <t>-2,36; 1,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,5; 8,14</t>
+          <t>0,06; 6,07</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 2,41</t>
+          <t>-0,25; 2,57</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 2,17</t>
+          <t>-0,35; 2,1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,96; 5,93</t>
+          <t>2,0; 6,01</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>7,88%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-0,4%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>238,59%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>inf%</t>
+          <t>251,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>713,59%</t>
+          <t>735,21%</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-44,86; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-42,08; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-62,47; —</t>
+          <t>-76,29; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-65,65; —</t>
+          <t>-76,23; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>118,33; —</t>
+          <t>99,73; —</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,46</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,68</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>0,03</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>0,48</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2,25</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,46</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,68</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,0</t>
+          <t>2,69</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,59</t>
+          <t>1,9</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 1,54</t>
+          <t>-1,79; 0,86</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 2,33</t>
+          <t>-0,9; 2,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,38; 4,63</t>
+          <t>-0,49; 3,14</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 0,76</t>
+          <t>-1,37; 1,53</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 2,83</t>
+          <t>-0,98; 2,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 2,78</t>
+          <t>0,54; 5,25</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 0,73</t>
+          <t>-1,19; 0,64</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 2,0</t>
+          <t>-0,53; 1,94</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,09</t>
+          <t>0,56; 3,53</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-51,82%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>76,4%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>133,67%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>4,9%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>67,06%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>317,48%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-51,82%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>76,4%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>111,88%</t>
+          <t>379,44%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>198,31%</t>
+          <t>235,8%</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-33,16; —</t>
+          <t>-52,02; 970,34</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-63,77; 1107,08</t>
+          <t>-10,61; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 247,78</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-63,71; 626,36</t>
+          <t>-52,49; 545,45</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>12,23; 950,74</t>
+          <t>15,74; 998,22</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0,51</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0,81</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2,52</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>1,79</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>0,53</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>2,57</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0,51</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0,81</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,36</t>
+          <t>2,88</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2,46</t>
+          <t>2,69</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,92</t>
+          <t>-0,46; 1,38</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 1,38</t>
+          <t>-0,01; 1,9</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,96</t>
+          <t>1,3; 3,88</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 1,51</t>
+          <t>0,76; 3,04</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 1,85</t>
+          <t>-0,29; 1,47</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,7</t>
+          <t>1,59; 4,58</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,0</t>
+          <t>0,51; 1,85</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,04; 1,36</t>
+          <t>0,04; 1,35</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,56; 3,44</t>
+          <t>1,69; 3,69</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>56,77%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>91,04%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>281,7%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>226,84%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>66,41%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>324,27%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>56,77%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>91,04%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>264,08%</t>
+          <t>364,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>291,23%</t>
+          <t>318,77%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>36,56; 625,38</t>
+          <t>-38,49; 260,01</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-41,22; 344,38</t>
+          <t>-9,53; 346,06</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>92,72; 916,96</t>
+          <t>90,5; 749,85</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-30,0; 276,77</t>
+          <t>48,72; 745,99</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 342,84</t>
+          <t>-28,3; 324,19</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,73; 683,46</t>
+          <t>109,52; 1001,72</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>38,29; 339,17</t>
+          <t>37,91; 316,97</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>0,36; 230,18</t>
+          <t>-3,66; 251,82</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>129,02; 596,11</t>
+          <t>159,21; 638,68</t>
         </is>
       </c>
     </row>
